--- a/output/pdf_financials_xlsx/ADE.xlsx
+++ b/output/pdf_financials_xlsx/ADE.xlsx
@@ -1366,16 +1366,16 @@
         <v>0.723455</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>0.947053</v>
+        <v>-0.947053</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>1.279508</v>
+        <v>-1.279508</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>0.767686</v>
+        <v>-0.767686</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>25.799699</v>
+        <v>-25.799699</v>
       </c>
       <c r="S16" s="1" t="inlineStr">
         <is>
@@ -1402,31 +1402,31 @@
         <v>-0.07133200000000001</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-0</v>
+        <v>-3.488708</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>-0.096301</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>-0</v>
+        <v>-3.520634</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>-0</v>
+        <v>-2.954748</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>-28.90291</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>-0</v>
+        <v>-1.845038</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>-0</v>
+        <v>-1.170904</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>-0</v>
+        <v>-1.535438</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>-0</v>
+        <v>-1.44691</v>
       </c>
       <c r="O17" s="3" t="n">
         <v>-0</v>
@@ -1656,46 +1656,46 @@
         <v>-1.677623</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>2.776585</v>
+        <v>-2.776585</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1.744354</v>
+        <v>-1.744354</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>1.637597</v>
+        <v>-1.637597</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>1.760317</v>
+        <v>-1.760317</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>1.477374</v>
+        <v>-1.477374</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>14.451455</v>
+        <v>-14.451455</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.922519</v>
+        <v>-0.922519</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0.585452</v>
+        <v>-0.585452</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>0.767719</v>
+        <v>-0.767719</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>0.723455</v>
+        <v>-0.723455</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>0.947053</v>
+        <v>-0.947053</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>1.279508</v>
+        <v>-1.279508</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>0.767686</v>
+        <v>-0.767686</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>25.799699</v>
+        <v>-25.799699</v>
       </c>
       <c r="S20" s="1" t="inlineStr">
         <is>
@@ -1845,46 +1845,46 @@
         <v>-1.677623</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>2.776585</v>
+        <v>-2.776585</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>1.744354</v>
+        <v>-1.744354</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>1.637597</v>
+        <v>-1.637597</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>1.760317</v>
+        <v>-1.760317</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>1.477374</v>
+        <v>-1.477374</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>14.451455</v>
+        <v>-14.451455</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>0.922519</v>
+        <v>-0.922519</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>0.585452</v>
+        <v>-0.585452</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>0.767719</v>
+        <v>-0.767719</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>0.723455</v>
+        <v>-0.723455</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>0.947053</v>
+        <v>-0.947053</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>1.279508</v>
+        <v>-1.279508</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>0.767686</v>
+        <v>-0.767686</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>25.799699</v>
+        <v>-25.799699</v>
       </c>
       <c r="S23" s="3" t="n">
         <v>-25.799699</v>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>138.82925</v>
+        <v>-138.82925</v>
       </c>
       <c r="F26" s="1" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
         </is>
       </c>
       <c r="J26" s="3" t="n">
-        <v>722.57275</v>
+        <v>-722.57275</v>
       </c>
       <c r="K26" s="1" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="R26" s="3" t="n">
-        <v>678.939447</v>
+        <v>-678.939447</v>
       </c>
       <c r="S26" s="1" t="inlineStr">
         <is>
@@ -2151,16 +2151,16 @@
         <v>0.723455</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>0.947053</v>
+        <v>-0.947053</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>1.279508</v>
+        <v>-1.279508</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>0.767686</v>
+        <v>-0.767686</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>25.799699</v>
+        <v>-25.799699</v>
       </c>
       <c r="S27" s="1" t="inlineStr">
         <is>
@@ -2277,16 +2277,16 @@
         <v>0.723455</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>0.947053</v>
+        <v>-0.947053</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>1.279508</v>
+        <v>-1.279508</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>0.767686</v>
+        <v>-0.767686</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>25.799699</v>
+        <v>-25.799699</v>
       </c>
       <c r="S29" s="1" t="inlineStr">
         <is>
@@ -2410,43 +2410,43 @@
         <v>2.63679589302738</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>6.248053586073019</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S31" s="1" t="inlineStr">
         <is>
@@ -34595,10 +34595,10 @@
         </is>
       </c>
       <c r="T251" s="5" t="n">
-        <v>0.767686</v>
+        <v>-0.767686</v>
       </c>
       <c r="U251" s="5" t="n">
-        <v>25.799699</v>
+        <v>-25.799699</v>
       </c>
       <c r="V251" t="inlineStr">
         <is>
@@ -35501,25 +35501,25 @@
         </is>
       </c>
       <c r="N260" s="5" t="n">
-        <v>0.922519</v>
+        <v>-0.922519</v>
       </c>
       <c r="O260" s="5" t="n">
-        <v>0.585452</v>
+        <v>-0.585452</v>
       </c>
       <c r="P260" s="5" t="n">
-        <v>0.767719</v>
+        <v>-0.767719</v>
       </c>
       <c r="Q260" s="5" t="n">
-        <v>0.723455</v>
+        <v>-0.723455</v>
       </c>
       <c r="R260" s="5" t="n">
-        <v>0.947053</v>
+        <v>-0.947053</v>
       </c>
       <c r="S260" s="5" t="n">
-        <v>1.279508</v>
+        <v>-1.279508</v>
       </c>
       <c r="T260" s="5" t="n">
-        <v>0.767686</v>
+        <v>-0.767686</v>
       </c>
       <c r="U260" t="inlineStr">
         <is>
@@ -37985,25 +37985,25 @@
         <v>-1.677623</v>
       </c>
       <c r="H285" s="5" t="n">
-        <v>2.776585</v>
+        <v>-2.776585</v>
       </c>
       <c r="I285" s="5" t="n">
-        <v>1.744354</v>
+        <v>-1.744354</v>
       </c>
       <c r="J285" s="5" t="n">
-        <v>1.637597</v>
+        <v>-1.637597</v>
       </c>
       <c r="K285" s="5" t="n">
-        <v>1.760317</v>
+        <v>-1.760317</v>
       </c>
       <c r="L285" s="5" t="n">
-        <v>1.477374</v>
+        <v>-1.477374</v>
       </c>
       <c r="M285" s="5" t="n">
-        <v>14.451455</v>
+        <v>-14.451455</v>
       </c>
       <c r="N285" s="5" t="n">
-        <v>0.922519</v>
+        <v>-0.922519</v>
       </c>
       <c r="O285" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/ADE.xlsx
+++ b/output/pdf_financials_xlsx/ADE.xlsx
@@ -955,28 +955,28 @@
         <v>1.399852</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1.714313</v>
+        <v>1.686976</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0</v>
+        <v>2.747642</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0</v>
+        <v>1.80746</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0</v>
+        <v>1.583017</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0</v>
+        <v>1.582172</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0</v>
+        <v>1.179902</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0</v>
+        <v>14.413146</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0</v>
+        <v>0.912586</v>
       </c>
       <c r="L10" s="3" t="n">
         <v>0</v>
@@ -1018,28 +1018,28 @@
         <v>-1.399852</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-1.714313</v>
+        <v>-1.686976</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>0</v>
+        <v>-2.747642</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0</v>
+        <v>-1.80746</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0</v>
+        <v>-1.583017</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>0</v>
+        <v>-1.582172</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>0</v>
+        <v>-1.179902</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0</v>
+        <v>-14.413146</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>0</v>
+        <v>-0.912586</v>
       </c>
       <c r="L11" s="3" t="n">
         <v>0</v>
@@ -1114,16 +1114,16 @@
         <v>0</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000616</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>-0.019058</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>-0.055986</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>-0.057288</v>
       </c>
       <c r="S12" s="1" t="inlineStr">
         <is>
@@ -2151,16 +2151,16 @@
         <v>0.723455</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.947053</v>
+        <v>-0.946437</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-1.279508</v>
+        <v>-1.26045</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-0.767686</v>
+        <v>-0.7117</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-25.799699</v>
+        <v>-25.742411</v>
       </c>
       <c r="S27" s="1" t="inlineStr">
         <is>
@@ -2277,16 +2277,16 @@
         <v>0.723455</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.947053</v>
+        <v>-0.946437</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-1.279508</v>
+        <v>-1.26045</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-0.767686</v>
+        <v>-0.7117</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-25.799699</v>
+        <v>-25.742411</v>
       </c>
       <c r="S29" s="1" t="inlineStr">
         <is>
@@ -2592,31 +2592,31 @@
         <v>0.035606</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.09493600000000001</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.076997</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.010505</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.038752</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.090224</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.08960799999999999</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.08372400000000001</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.200733</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>0.225116</v>
       </c>
     </row>
     <row r="35">
@@ -2714,31 +2714,31 @@
         <v>0.035606</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.09493600000000001</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.076997</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.010505</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.038752</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.090224</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.08960799999999999</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.08372400000000001</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.200733</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0</v>
+        <v>0.225116</v>
       </c>
     </row>
     <row r="37">
@@ -3446,31 +3446,31 @@
         <v>0.130185</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.175901</v>
+        <v>0.080965</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.154547</v>
+        <v>0.07754999999999999</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.038307</v>
+        <v>0.027802</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.064202</v>
+        <v>0.02545</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.11855</v>
+        <v>0.028326</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.123203</v>
+        <v>0.033595</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.170383</v>
+        <v>0.086659</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.257936</v>
+        <v>0.057203</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>0.295077</v>
+        <v>0.069961</v>
       </c>
     </row>
     <row r="49">
@@ -8106,16 +8106,16 @@
         <v>0</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>0</v>
+        <v>-0.010484</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0</v>
+        <v>-0.022969</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>0</v>
+        <v>-0.024628</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>0</v>
+        <v>-0.0174</v>
       </c>
       <c r="G124" s="3" t="n">
         <v>0</v>
@@ -8167,16 +8167,16 @@
         <v>0</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0</v>
+        <v>-0.010484</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0</v>
+        <v>-0.022969</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>0</v>
+        <v>-0.024628</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>0</v>
+        <v>-0.0174</v>
       </c>
       <c r="G125" s="3" t="n">
         <v>0</v>
@@ -9014,7 +9014,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -29516,7 +29516,11 @@
           <t>Finance lease payments</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr"/>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E204" t="inlineStr">
         <is>
           <t>-</t>
@@ -32156,7 +32160,11 @@
           <t>Capital lease payments</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr"/>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E229" t="inlineStr">
         <is>
           <t>-</t>
@@ -33870,7 +33878,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -35248,7 +35256,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -37282,7 +37290,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">

--- a/output/pdf_financials_xlsx/ADE.xlsx
+++ b/output/pdf_financials_xlsx/ADE.xlsx
@@ -2175,46 +2175,46 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0</v>
+        <v>0.009214999999999999</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0</v>
+        <v>0.015715</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>0.03022</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0</v>
+        <v>0.067161</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>0.050042</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0</v>
+        <v>0.024274</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0</v>
+        <v>0.018895</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0</v>
+        <v>0.006221</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0</v>
+        <v>0.006011</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
+        <v>0.006011</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0</v>
+        <v>0.006011</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0</v>
+        <v>0.006011</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0</v>
+        <v>0.006011</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0</v>
+        <v>0.005395</v>
       </c>
       <c r="P28" s="3" t="n">
         <v>0</v>
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>0</v>
+        <v>0.00575</v>
       </c>
       <c r="S28" s="1" t="inlineStr">
         <is>
@@ -2238,46 +2238,46 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-3.701038</v>
+        <v>-3.691823</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.399852</v>
+        <v>-1.384137</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.677623</v>
+        <v>-1.647403</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>2.705253</v>
+        <v>2.772414</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>1.744354</v>
+        <v>1.794396</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>1.541296</v>
+        <v>1.56557</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>1.760317</v>
+        <v>1.779212</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1.477374</v>
+        <v>1.483595</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>14.451455</v>
+        <v>14.457466</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.922519</v>
+        <v>0.92853</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.585452</v>
+        <v>0.591463</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>0.767719</v>
+        <v>0.77373</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>0.723455</v>
+        <v>0.7294659999999999</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.946437</v>
+        <v>-0.941042</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>-1.26045</v>
@@ -2286,7 +2286,7 @@
         <v>-0.7117</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-25.742411</v>
+        <v>-25.736661</v>
       </c>
       <c r="S29" s="1" t="inlineStr">
         <is>
@@ -6639,46 +6639,46 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>0.009214999999999999</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.015715</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.03022</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.067161</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.050042</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>0.024274</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>0.018895</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>0.006221</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>0.006011</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>0.006011</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>0.006011</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>0.006011</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>0.006011</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>0.005395</v>
       </c>
       <c r="P100" s="3" t="n">
         <v>0</v>
@@ -6687,10 +6687,10 @@
         <v>0</v>
       </c>
       <c r="R100" s="3" t="n">
-        <v>0</v>
+        <v>0.00575</v>
       </c>
       <c r="S100" s="3" t="n">
-        <v>0</v>
+        <v>0.00575</v>
       </c>
     </row>
     <row r="101">
@@ -20928,7 +20928,11 @@
           <t>Depreciation of property, plant and equipment (note 5)</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
           <t>-</t>
@@ -23496,7 +23500,11 @@
           <t>Depreciation of property, plant and equipment (note 5)</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr"/>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E145" t="inlineStr">
         <is>
           <t>-</t>
@@ -27116,7 +27124,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr"/>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E180" s="5" t="n">
         <v>0.009214999999999999</v>
       </c>

--- a/output/pdf_financials_xlsx/ADE.xlsx
+++ b/output/pdf_financials_xlsx/ADE.xlsx
@@ -4451,46 +4451,46 @@
         <v>0</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.183381</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>0.524708</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>0.53206</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>0.153982</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>0.434907</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>0.626753</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>0.084648</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>0</v>
+        <v>0.116863</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>0</v>
+        <v>0.131918</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>0</v>
+        <v>0.126494</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>0</v>
+        <v>0.114891</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>0</v>
+        <v>0.087323</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>0</v>
+        <v>0.036085</v>
       </c>
       <c r="S64" s="3" t="n">
-        <v>0</v>
+        <v>0.163752</v>
       </c>
     </row>
     <row r="65">
@@ -4634,46 +4634,46 @@
         <v>0</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.16186</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.227412</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.313628</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.208981</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.170573</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.189342</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.346075</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.5756019999999999</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.088487</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.09164799999999999</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>0.117935</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>0.023978</v>
       </c>
       <c r="R67" s="3" t="n">
-        <v>0</v>
+        <v>0.036295</v>
       </c>
       <c r="S67" s="3" t="n">
-        <v>0</v>
+        <v>0.052928</v>
       </c>
     </row>
     <row r="68">
@@ -31960,7 +31960,11 @@
           <t>Future income taxes</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr"/>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E227" t="inlineStr">
         <is>
           <t>-</t>
